--- a/data-raw/public-site/moa-genetic-resource/xlsx/list-year-2024-batch-03.xlsx
+++ b/data-raw/public-site/moa-genetic-resource/xlsx/list-year-2024-batch-03.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\techme\data-raw\public-site\moa-genetic-resource\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEBCA187-4411-4A09-BA44-77A62548A3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4E1EC4-7CD4-43F0-8602-7E8C43AA5684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-6885" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="51480" yWindow="5070" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="67">
   <si>
     <t>year</t>
   </si>
@@ -164,6 +164,283 @@
       </rPr>
       <t>（新疆）</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>畜禽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>国家北京油鸡保</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>种场</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>北京市农林科</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>学院</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>国家蒙古牛保种场</t>
+  </si>
+  <si>
+    <t>苏尼特左旗原种畜牧业发展有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>国家吉林梅花鹿保</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>种场</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长春市东大鹿业有限公司</t>
+  </si>
+  <si>
+    <t>国家中蜂(华中中蜂)保种场</t>
+  </si>
+  <si>
+    <t>苏州元丰蜂种有限公司</t>
+  </si>
+  <si>
+    <t>国家皖西白鹅保种场</t>
+  </si>
+  <si>
+    <r>
+      <t>六</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>安安皋养殖有限公司</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>国家中蜂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>华南中蜂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>保种场</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>泾县永春养蜂专业合作社</t>
+  </si>
+  <si>
+    <t>国家小尾寒羊保种场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>泰安市同成牧业有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>国家济宁青山羊保种场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>曹县正道牧业科技有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>国家豁眼鹅保种场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>青岛鑫河畜禽良种繁育场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>国家大足黑山羊保种场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重庆市大足区瑞丰现代农业发展有限公司</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>国</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>家四川白鹅保种场</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重庆泰华牧业(集团)有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四川恒通内江猪保种繁育有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>国家长顺绿壳蛋鸡保种场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>国家内江猪保种场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长顺天农绿壳蛋鸡实业有限公司</t>
+  </si>
+  <si>
+    <t>北京</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吉林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江苏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安徽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重庆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贵州</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -171,7 +448,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -208,6 +485,14 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -229,11 +514,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -530,7 +816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="51.5703125" bestFit="1" customWidth="1"/>
@@ -721,6 +1007,305 @@
         <v>28</v>
       </c>
     </row>
+    <row r="9" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>2024</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>2024</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>2024</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2024</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>2024</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>2024</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14">
+        <v>6</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>2024</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15">
+        <v>7</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>2024</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16">
+        <v>8</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>2024</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17">
+        <v>9</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>2024</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18">
+        <v>10</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19">
+        <v>11</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>2024</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20">
+        <v>12</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>2024</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21">
+        <v>13</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data-raw/public-site/moa-genetic-resource/xlsx/list-year-2024-batch-03.xlsx
+++ b/data-raw/public-site/moa-genetic-resource/xlsx/list-year-2024-batch-03.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\techme\data-raw\public-site\moa-genetic-resource\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4E1EC4-7CD4-43F0-8602-7E8C43AA5684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F442322-F52F-42B1-BF45-A61C3D593EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51480" yWindow="5070" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -174,10 +174,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>畜禽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -441,6 +437,10 @@
   </si>
   <si>
     <t>贵州</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>畜禽保种场</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1015,19 +1015,19 @@
         <v>32</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
@@ -1038,19 +1038,19 @@
         <v>32</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D10">
         <v>2</v>
       </c>
       <c r="E10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="G10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
@@ -1061,19 +1061,19 @@
         <v>31</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" t="s">
         <v>38</v>
       </c>
-      <c r="F11" t="s">
-        <v>39</v>
-      </c>
       <c r="G11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1084,19 +1084,19 @@
         <v>31</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D12">
         <v>4</v>
       </c>
       <c r="E12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" t="s">
         <v>40</v>
       </c>
-      <c r="F12" t="s">
-        <v>41</v>
-      </c>
       <c r="G12" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
@@ -1107,19 +1107,19 @@
         <v>31</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D13">
         <v>5</v>
       </c>
       <c r="E13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="G13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
@@ -1130,19 +1130,19 @@
         <v>31</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D14">
         <v>6</v>
       </c>
       <c r="E14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" t="s">
         <v>44</v>
       </c>
-      <c r="F14" t="s">
-        <v>45</v>
-      </c>
       <c r="G14" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
@@ -1153,16 +1153,16 @@
         <v>31</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D15">
         <v>7</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>12</v>
@@ -1176,16 +1176,16 @@
         <v>31</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D16">
         <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>12</v>
@@ -1199,16 +1199,16 @@
         <v>31</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D17">
         <v>9</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>12</v>
@@ -1222,19 +1222,19 @@
         <v>31</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D18">
         <v>10</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" t="s">
         <v>52</v>
       </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
       <c r="G18" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
@@ -1245,19 +1245,19 @@
         <v>31</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D19">
         <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="G19" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
@@ -1268,16 +1268,16 @@
         <v>31</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D20">
         <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>22</v>
@@ -1291,19 +1291,19 @@
         <v>31</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D21">
         <v>13</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
